--- a/DSA-Sheets/DSA patterns Cheat Sheet.xlsx
+++ b/DSA-Sheets/DSA patterns Cheat Sheet.xlsx
@@ -5,22 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Documents\Data_Scientist\DSA\DSA-Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67565A33-7C2D-43D6-961E-7AED4FAD9490}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4FCBD9-C643-4887-B04A-00EAC19DFD9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="397">
   <si>
     <t>INSTA Channel. One question Daily</t>
   </si>
@@ -4134,7 +4134,9 @@
       <c r="E123" s="8"/>
     </row>
     <row r="124" spans="1:5" ht="14.5">
-      <c r="A124" s="6"/>
+      <c r="A124" s="6" t="s">
+        <v>396</v>
+      </c>
       <c r="B124" s="15" t="s">
         <v>228</v>
       </c>
